--- a/public/templates/Fletedergese-Shabllon-Pozicione.xlsx
+++ b/public/templates/Fletedergese-Shabllon-Pozicione.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\AAB\Viti 3 Semestri 6\Tema-Graniti\Fatura\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\AAB\Viti 3 Semestri 6\Tema-Graniti\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D54444-F619-4B21-B1A3-C11DB22A8402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54721B8F-020D-4C89-B965-81F1EDA73B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -228,7 +228,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,111 +266,104 @@
     <font>
       <sz val="22"/>
       <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="22"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="26"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="26"/>
+      <sz val="11"/>
+      <color rgb="FF1C1C1C"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color rgb="FFFF3300"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color rgb="FFFF6600"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color rgb="FF4D4D4D"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1C1C1C"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="36"/>
-      <color rgb="FFFF3300"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="36"/>
-      <color rgb="FFFF6600"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="36"/>
-      <color rgb="FF4D4D4D"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <u/>
       <sz val="14"/>
@@ -387,29 +380,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -689,35 +659,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -725,99 +684,90 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -829,26 +779,29 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1324,13 +1277,13 @@
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1340,12 +1293,12 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1355,326 +1308,328 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="J10" s="26" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="J10" s="21" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:10" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
-      <c r="G12" s="32" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17"/>
+      <c r="G12" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="16"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="14"/>
     </row>
     <row r="13" spans="1:10" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="57"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="25"/>
-      <c r="G14" s="34" t="s">
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="49"/>
+      <c r="G13" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="36"/>
-    </row>
-    <row r="15" spans="1:10" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="s">
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="31"/>
+    </row>
+    <row r="14" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="19"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="20"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="31"/>
+    </row>
+    <row r="15" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="60"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="51"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="52"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="31"/>
     </row>
     <row r="16" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A16" s="24"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="23"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="54"/>
+      <c r="E16" s="18"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="63"/>
-      <c r="G17" s="37" t="s">
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="55"/>
+      <c r="G17" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="39"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="34"/>
     </row>
     <row r="18" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:10" ht="21" x14ac:dyDescent="0.4">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="48"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="43"/>
     </row>
     <row r="20" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="42"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="37"/>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="40"/>
     </row>
     <row r="22" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="64"/>
-      <c r="C23" s="64" t="s">
+      <c r="B23" s="56"/>
+      <c r="C23" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64" t="s">
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="H23" s="64" t="s">
+      <c r="H23" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="64" t="s">
+      <c r="I23" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="64" t="s">
+      <c r="J23" s="56" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="64"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
+      <c r="A24" s="56"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="56"/>
     </row>
     <row r="25" spans="1:10" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="65">
+      <c r="A25" s="57">
         <v>1</v>
       </c>
-      <c r="B25" s="65"/>
-      <c r="C25" s="66" t="s">
+      <c r="B25" s="57"/>
+      <c r="C25" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="28" t="s">
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="24">
         <v>82.5</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="24">
         <v>9</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="26">
         <f>(H25*I25)</f>
         <v>742.5</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="65">
+      <c r="A26" s="57">
         <v>2</v>
       </c>
-      <c r="B26" s="65"/>
-      <c r="C26" s="66" t="s">
+      <c r="B26" s="57"/>
+      <c r="C26" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="28" t="s">
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="24">
         <v>1</v>
       </c>
-      <c r="I26" s="29">
+      <c r="I26" s="24">
         <v>97.5</v>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="26">
         <f t="shared" ref="J26:J28" si="0">(H26*I26)</f>
         <v>97.5</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="65">
+      <c r="A27" s="57">
         <v>3</v>
       </c>
-      <c r="B27" s="65"/>
-      <c r="C27" s="66" t="s">
+      <c r="B27" s="57"/>
+      <c r="C27" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="28" t="s">
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="29">
+      <c r="H27" s="24">
         <v>2</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I27" s="24">
         <v>20</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="26">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="65">
+      <c r="A28" s="57">
         <v>4</v>
       </c>
-      <c r="B28" s="65"/>
-      <c r="C28" s="66" t="s">
+      <c r="B28" s="57"/>
+      <c r="C28" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="28" t="s">
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="24">
         <v>5</v>
       </c>
-      <c r="I28" s="29">
+      <c r="I28" s="24">
         <v>20</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="26">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="65"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="30" t="s">
+      <c r="A29" s="57"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J29" s="31">
+      <c r="J29" s="26">
         <f>SUM(J25:J28)</f>
         <v>980</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="J31" s="5" t="s">
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="J31" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
+    <row r="32" spans="1:10" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
     </row>
     <row r="33" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -1695,16 +1650,16 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G14:J14"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="A20:I21"/>
     <mergeCell ref="A19:I19"/>
-    <mergeCell ref="G15:J15"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A17:E17"/>
+    <mergeCell ref="G13:J15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="79" fitToHeight="0" orientation="portrait" r:id="rId1"/>
